--- a/artfynd/A 57802-2023 artfynd.xlsx
+++ b/artfynd/A 57802-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57802-2023 artfynd.xlsx
+++ b/artfynd/A 57802-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>126815007</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>126815012</v>
       </c>
       <c r="B4" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>126815011</v>
       </c>
       <c r="B5" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57802-2023 artfynd.xlsx
+++ b/artfynd/A 57802-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>126815007</v>
       </c>
       <c r="B3" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>126815012</v>
       </c>
       <c r="B4" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>126815011</v>
       </c>
       <c r="B5" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57802-2023 artfynd.xlsx
+++ b/artfynd/A 57802-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>126815007</v>
       </c>
       <c r="B3" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57802-2023 artfynd.xlsx
+++ b/artfynd/A 57802-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>126815007</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>126815012</v>
       </c>
       <c r="B4" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>126815011</v>
       </c>
       <c r="B5" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57802-2023 artfynd.xlsx
+++ b/artfynd/A 57802-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>126815007</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>126815012</v>
       </c>
       <c r="B4" t="n">
-        <v>78685</v>
+        <v>78678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>126815011</v>
       </c>
       <c r="B5" t="n">
-        <v>78685</v>
+        <v>78678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
